--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487488_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487488_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>15.4506</v>
+        <v>14.7545</v>
       </c>
       <c r="E2" t="n">
-        <v>16.8188</v>
+        <v>16.6306</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3682</v>
+        <v>-1.8761</v>
       </c>
       <c r="G2" t="n">
         <v>9.917199999999999</v>
@@ -610,13 +610,13 @@
         <v>3.7211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3501</v>
+        <v>-0.346</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3582</v>
+        <v>-0.5464</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7083</v>
+        <v>0.2004</v>
       </c>
       <c r="V2" t="n">
         <v>6.3584</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7302</v>
+        <v>1.304</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3444</v>
+        <v>3.2389</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6142</v>
+        <v>-1.9349</v>
       </c>
       <c r="G3" t="n">
         <v>-3.1609</v>
@@ -688,13 +688,13 @@
         <v>3.7211</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.246</v>
+        <v>-0.6722</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.7821</v>
+        <v>-0.8875</v>
       </c>
       <c r="U3" t="n">
-        <v>0.536</v>
+        <v>0.2153</v>
       </c>
       <c r="V3" t="n">
         <v>3.3745</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>X. FOLCH CLARAMUNT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.598</v>
+        <v>-0.8566</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8672</v>
+        <v>0.2378</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4652</v>
+        <v>-1.0944</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6337</v>
+        <v>-1.4172</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.346</v>
+        <v>-0.4825</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2877</v>
+        <v>-0.9347</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3037</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0.0612</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2425</v>
+        <v>0.0048</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9375</v>
+        <v>-1.4833</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4073</v>
+        <v>-0.5437</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5302</v>
+        <v>-0.9396</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.1689</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5634</v>
+        <v>0.1717</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1013</v>
+        <v>-0.0028</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3686</v>
+        <v>-0.8783</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8935</v>
+        <v>0.5602</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2621</v>
+        <v>-1.4385</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.199</v>
+        <v>-0.6337</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.067</v>
+        <v>-0.346</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.132</v>
+        <v>-0.2877</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9748</v>
+        <v>0.3037</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0412</v>
+        <v>0.0612</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0664</v>
+        <v>0.2425</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1738</v>
+        <v>-0.9375</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.1082</v>
+        <v>-0.4073</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0656</v>
+        <v>-0.5302</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.445</v>
+        <v>0.3845</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.594</v>
+        <v>0.2564</v>
       </c>
       <c r="U5" t="n">
-        <v>0.149</v>
+        <v>0.1281</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8837</v>
+        <v>-1.2166</v>
       </c>
       <c r="W5" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. FOLCH CLARAMUNT</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4649</v>
+        <v>-0.9963</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2903</v>
+        <v>1.3193</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1746</v>
+        <v>-2.3156</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4172</v>
+        <v>-2.199</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4825</v>
+        <v>-1.067</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9347</v>
+        <v>-1.132</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.9748</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0612</v>
+        <v>1.0412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0048</v>
+        <v>-0.0664</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4833</v>
+        <v>-3.1738</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5437</v>
+        <v>-2.1082</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9396</v>
+        <v>-1.0656</v>
       </c>
       <c r="P6" t="n">
         <v>0.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4394</v>
+        <v>-0.0726</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3564</v>
+        <v>-0.1682</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.083</v>
+        <v>0.0956</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. LOPEZ SANJURJO</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.276</v>
+        <v>-2.3626</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7762</v>
+        <v>-1.5584</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0523</v>
+        <v>-0.8042</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6285</v>
+        <v>-2.5436</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9466</v>
+        <v>-0.8714</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6819</v>
+        <v>-1.6722</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8068</v>
+        <v>-1.202</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6856</v>
+        <v>-0.6006</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1212</v>
+        <v>-0.6014</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4353</v>
+        <v>-1.3416</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6322</v>
+        <v>-0.2708</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8031</v>
+        <v>-1.0708</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7649</v>
+        <v>-0.4065</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9487</v>
+        <v>-0.3564</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1838</v>
+        <v>-0.0501</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4963</v>
+        <v>-2.3923</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5584</v>
+        <v>-1.6333</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9379</v>
+        <v>-0.759</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5436</v>
+        <v>-2.3886</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8714</v>
+        <v>-2.4594</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6722</v>
+        <v>0.0708</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.202</v>
+        <v>-1.7834</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6006</v>
+        <v>-1.9855</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6014</v>
+        <v>0.2021</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3416</v>
+        <v>-0.6052</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2708</v>
+        <v>-0.4739</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0708</v>
+        <v>-0.1313</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5402</v>
+        <v>-0.4335</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3564</v>
+        <v>-0.1253</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1838</v>
+        <v>-0.3082</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.9412</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6204</v>
+        <v>-2.4611</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6308</v>
+        <v>-0.819</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9896</v>
+        <v>-1.6421</v>
       </c>
       <c r="G9" t="n">
         <v>-4.3274</v>
@@ -1156,13 +1156,13 @@
         <v>3.1336</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9981</v>
+        <v>-0.8388</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0612</v>
+        <v>-0.2494</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.5895</v>
       </c>
       <c r="V9" t="n">
         <v>0.5507</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>E. LOPEZ SANJURJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9086</v>
+        <v>-2.697</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0426</v>
+        <v>0.2216</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8659</v>
+        <v>-2.9186</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3886</v>
+        <v>-1.6285</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4594</v>
+        <v>-0.9466</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0708</v>
+        <v>-0.6819</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7834</v>
+        <v>0.8068</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9855</v>
+        <v>0.6856</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2021</v>
+        <v>0.1212</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6052</v>
+        <v>-2.4353</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4739</v>
+        <v>-1.6322</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1313</v>
+        <v>-0.8031</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3709</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q10" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.0501</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.2166</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3709</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.9497</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.5346</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.4151</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.9412</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2166</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8942</v>
+        <v>-3.7486</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7885</v>
+        <v>-2.6697</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1057</v>
+        <v>-1.0789</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9055</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5762</v>
+        <v>-0.4307</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2088</v>
+        <v>-0.09</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3674</v>
+        <v>-0.3407</v>
       </c>
       <c r="V11" t="n">
         <v>0.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7312</v>
+        <v>-4.952</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0379</v>
+        <v>-1.2856</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6932</v>
+        <v>-3.6665</v>
       </c>
       <c r="G12" t="n">
         <v>-3.425</v>
@@ -1390,13 +1390,13 @@
         <v>0.9792</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1478</v>
+        <v>-0.0731</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0306</v>
+        <v>-0.2782</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1784</v>
+        <v>0.2051</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4332</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.177400000000002</v>
+        <v>-5.286300000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>13.3516</v>
+        <v>14.2424</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.5289</v>
+        <v>-19.5288</v>
       </c>
       <c r="G13" t="n">
         <v>-16.7122</v>
@@ -1447,7 +1447,7 @@
         <v>5.0777</v>
       </c>
       <c r="L13" t="n">
-        <v>9.213800000000001</v>
+        <v>9.213799999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-31.0039</v>
@@ -1468,16 +1468,16 @@
         <v>18.6054</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.267</v>
+        <v>-2.3761</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.7702</v>
+        <v>-1.8793</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4971</v>
+        <v>-0.4969</v>
       </c>
       <c r="V13" t="n">
-        <v>5.967999999999998</v>
+        <v>5.968</v>
       </c>
       <c r="W13" t="n">
         <v>12.6017</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4603</v>
+        <v>6.474</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3092</v>
+        <v>7.0022</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8489</v>
+        <v>-0.5282</v>
       </c>
       <c r="G14" t="n">
         <v>6.2851</v>
@@ -1546,13 +1546,13 @@
         <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>0.742</v>
+        <v>0.7558</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5505</v>
+        <v>0.2435</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1915</v>
+        <v>0.5123</v>
       </c>
       <c r="V14" t="n">
         <v>0.6083</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7532</v>
+        <v>4.2031</v>
       </c>
       <c r="E15" t="n">
-        <v>6.5612</v>
+        <v>6.6636</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.808</v>
+        <v>-2.4605</v>
       </c>
       <c r="G15" t="n">
         <v>6.2087</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1006</v>
+        <v>0.3492</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0465</v>
+        <v>0.1488</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1471</v>
+        <v>0.2004</v>
       </c>
       <c r="V15" t="n">
         <v>-1.7673</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1654</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0767</v>
+        <v>0.337</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0888</v>
+        <v>0.5274</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2709</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9409</v>
+        <v>1.6399</v>
       </c>
       <c r="T16" t="n">
-        <v>2.4784</v>
+        <v>0.7387</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4625</v>
+        <v>0.9012</v>
       </c>
       <c r="V16" t="n">
         <v>2.4332</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2746</v>
+        <v>0.577</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7442</v>
+        <v>3.1535</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4696</v>
+        <v>-2.5765</v>
       </c>
       <c r="G17" t="n">
         <v>4.2976</v>
@@ -1780,13 +1780,13 @@
         <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4148</v>
+        <v>-0.1123</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7546</v>
+        <v>-0.3452</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3398</v>
+        <v>0.2329</v>
       </c>
       <c r="V17" t="n">
         <v>-2.4332</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8933</v>
+        <v>0.224</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4033</v>
+        <v>3.1197</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2966</v>
+        <v>-2.8957</v>
       </c>
       <c r="G18" t="n">
         <v>2.0352</v>
@@ -1858,13 +1858,13 @@
         <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7119</v>
+        <v>0.4054</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.102</v>
+        <v>0.503</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8249</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9619</v>
+        <v>-1.9398</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5966</v>
+        <v>-0.4943</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3653</v>
+        <v>-1.4455</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7166</v>
@@ -1936,13 +1936,13 @@
         <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1658</v>
+        <v>-0.1437</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3564</v>
+        <v>-0.2541</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1906</v>
+        <v>0.1104</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2754</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6208</v>
+        <v>-4.2252</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9692</v>
+        <v>-0.2529</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6516</v>
+        <v>-3.9724</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1269</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0227</v>
+        <v>0.3729</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6534</v>
+        <v>0.0629</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6307</v>
+        <v>0.31</v>
       </c>
       <c r="V20" t="n">
         <v>-2.7086</v>
@@ -2053,7 +2053,7 @@
         <v>19.5288</v>
       </c>
       <c r="F21" t="n">
-        <v>-13.3512</v>
+        <v>-13.3514</v>
       </c>
       <c r="G21" t="n">
         <v>16.7122</v>
@@ -2092,13 +2092,13 @@
         <v>10.7715</v>
       </c>
       <c r="S21" t="n">
-        <v>3.267100000000001</v>
+        <v>3.2672</v>
       </c>
       <c r="T21" t="n">
         <v>0.4970000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>2.77</v>
+        <v>2.7702</v>
       </c>
       <c r="V21" t="n">
         <v>-5.9679</v>
